--- a/李涛绩效_已填写 (1).xlsx
+++ b/李涛绩效_已填写 (1).xlsx
@@ -1,389 +1,223 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7670"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="18350" windowHeight="7670" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="李涛自评" sheetId="1" r:id="rId1"/>
+    <sheet name="李涛自评" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>指标
-类型</t>
-  </si>
-  <si>
-    <t>部门</t>
-  </si>
-  <si>
-    <t>人员</t>
-  </si>
-  <si>
-    <t>考核指标</t>
-  </si>
-  <si>
-    <t>年度目标</t>
-  </si>
-  <si>
-    <t>评价等级（每个等级对应目标）</t>
-  </si>
-  <si>
-    <t>权重
-比例</t>
-  </si>
-  <si>
-    <t>数据来源</t>
-  </si>
-  <si>
-    <t>完成情况</t>
-  </si>
-  <si>
-    <t>实际得分</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>A（120%）</t>
-  </si>
-  <si>
-    <t>B（100%）</t>
-  </si>
-  <si>
-    <t>C（90%）</t>
-  </si>
-  <si>
-    <t>D（80%）</t>
-  </si>
-  <si>
-    <t>E（0）</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>李涛</t>
-  </si>
-  <si>
-    <t>Sandwich项目管理支持</t>
-  </si>
-  <si>
-    <t>1）连续氢化建设项目管理支持：
-目前项目已推进至 HAZOP 完成阶段。2026年将持续支持并协调 CFCT、IEPE 与 SW 各方，推进布局设计、工程采购、CE认证、测试验证等工作，做好跨团队沟通与协同，保障项目按计划整体推进。</t>
-  </si>
-  <si>
-    <t>完成年度目标，自评结合上级评价【加分上限为指标权重的20%】</t>
-  </si>
-  <si>
-    <t>自评+上级领导审核</t>
-  </si>
-  <si>
-    <t>作为国内项目管理支持，协调 CFCT、IEPE 与 UK Sandwich 三方，系统推动项目整体节奏，主要进展如下：
-• 已推动关闭三方之间 30 余项关键设计议题（含 PFD / P&amp;ID / URS 三大设计文件对齐、SE01 气液分离器方案闭环、CE-MD 认证范围确定、防爆区域划分方向确定等），主要设计文件基本齐备；
-• 建立并稳定运行中英双方的技术协作机制，通过双语《会议纪要跟踪表》系统跟踪超过 100 项议题，对英方问询、技术分歧、设计变更做到全过程可追溯；
-• 有效应对超临界流体安全阀泄放计算等前沿技术议题，组织国内技术团队与 UK 同行建立对等技术对话，避免项目在关键节点上被动等待；
-• 设计基线对齐工作 —— 汇总国内 33 项待澄清问题与 UK 一方 59 项 Risk Register 合并至统一跟踪；
-下半年计划：继续推动详细设计完成、主设备采购启动、CE 认证正式启动，为 2027 年 FAT 与现场开车目标铺路。项目整体节奏可控。</t>
-  </si>
-  <si>
-    <t>项目按计划推进，超期风险已受控</t>
-  </si>
-  <si>
-    <t>2）HPLC和冻干机建设项目管理支持：
-目前项目已完成可行性研究及投资框架梳理。2026年将持续支持并协调工程设备部与 SW 方，推进下阶段设计、长周期设备采购决策及相关配套事项对接，保障项目有序实施。</t>
-  </si>
-  <si>
-    <t>作为国内项目管理支持，协调工程设备部与 UK Sandwich 两方，系统推动制备色谱及冻干机改造项目节奏，主要进展如下：
-• 全程跟进英国侧可行性研究讲解及多轮专题会，推动方案布局与投资口径在英方与国内团队之间形成一致理解，可行性研究结论及投资框架已明确；
-• 汇总项目投资与进度信息，编制多版组合汇报材料，支撑汇报与下阶段决策沟通；
-• 持续跟进设备供货与方案变更确认，协调国内团队经验输入，并统筹色谱冻干改造与 C1 模块升级、高活实验室等配套事项的接口对接，避免各子项割裂推进；</t>
-  </si>
-  <si>
-    <t>项目处于早期阶段，按计划推进</t>
-  </si>
-  <si>
-    <t>3）902贴建项目管理支持：
-目前项目已完成东侧扩建可行性研究（2026年5月）。2026年将持续支持并协调工程设备部与 SW 方，推进概念设计、关键方案确认及与国内团队的信息闭环，确保项目按计划开展。</t>
-  </si>
-  <si>
-    <t>作为国内项目管理支持，协调工程设备部与 UK Sandwich 及设计方，系统推动 902 东侧扩建项目节奏，主要进展如下：
-• 全程参与可行性研究讲解会，整理中文详细纪要及对内通报材料，推动国内团队理解推荐方案及关键前提假设；
-• 协助完成投资量级、风险与总控计划的梳理解读，编制汇报材料，支撑扩建项目投资与进度决策；</t>
-  </si>
-  <si>
-    <t>Sandwich 相关支持任务</t>
-  </si>
-  <si>
-    <t>负责 Sandwich 站点年度预算申请、执行监控及回顾，并协调机器学习研讨小组，推动相关技术交流与协作落地</t>
-  </si>
-  <si>
-    <t>月概算和月回顾100%完成</t>
-  </si>
-  <si>
-    <t>100%＞完成率≥90%</t>
-  </si>
-  <si>
-    <t>90%＞完成率≥80%</t>
-  </si>
-  <si>
-    <t>80%＞完成率≥70%</t>
-  </si>
-  <si>
-    <t>完成率＜70%</t>
-  </si>
-  <si>
-    <t>承担 Sandwich 站点预算及机器学习研讨小组相关支持，主要进展如下：
-• 参与 Sandwich 站点年度预算申请、执行跟踪相关数据整理与内外沟通支持；
-• 协调机器学习研讨小组交流安排，推动相关技术议题按计划开展；</t>
-  </si>
-  <si>
-    <t>月概算与月回顾按时 100% 完成</t>
-  </si>
-  <si>
-    <t>重点工作</t>
-  </si>
-  <si>
-    <t>配合推进电算化等生产管理重点工作。
-支持生产管理重点工作的落实，全力推动，确保各项工作顺利开展。</t>
-  </si>
-  <si>
-    <t>按上级安排配合推进</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="177" formatCode="[$-409]mmm;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="[$-409]mmm;@"/>
   </numFmts>
   <fonts count="27">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -587,7 +421,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -771,231 +605,281 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="11">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="34">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="52">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="52">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="53">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="50">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="51">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1056,17 +940,80 @@
     <cellStyle name="常规 103 4 2 7 2" xfId="53"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="指标清单"/>
       <sheetName val="汇总-中期"/>
@@ -5961,303 +5908,437 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:Q8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="2.26363636363636" customWidth="1"/>
-    <col min="2" max="2" width="4.72727272727273" customWidth="1"/>
-    <col min="3" max="3" width="5.86363636363636" customWidth="1"/>
-    <col min="5" max="5" width="7.46363636363636" customWidth="1"/>
-    <col min="6" max="6" width="10.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="45.4" customWidth="1"/>
-    <col min="8" max="12" width="11.4" customWidth="1"/>
-    <col min="13" max="13" width="5.72727272727273" customWidth="1"/>
-    <col min="14" max="14" width="12.2636363636364" customWidth="1"/>
-    <col min="15" max="15" width="56.8181818181818" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="26" customWidth="1"/>
+    <col width="2.26363636363636" customWidth="1" min="1" max="1"/>
+    <col width="4.72727272727273" customWidth="1" min="2" max="2"/>
+    <col width="5.86363636363636" customWidth="1" min="3" max="3"/>
+    <col width="7.46363636363636" customWidth="1" min="5" max="5"/>
+    <col width="10.7272727272727" customWidth="1" min="6" max="6"/>
+    <col width="45.4" customWidth="1" min="7" max="7"/>
+    <col width="11.4" customWidth="1" min="8" max="12"/>
+    <col width="5.72727272727273" customWidth="1" min="13" max="13"/>
+    <col width="12.2636363636364" customWidth="1" min="14" max="14"/>
+    <col width="56.8181818181818" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.65" customHeight="1" spans="2:17">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
+    <row r="2" ht="14.65" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>指标
+类型</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>部门</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>人员</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>考核指标</t>
+        </is>
+      </c>
+      <c r="G2" s="27" t="inlineStr">
+        <is>
+          <t>年度目标</t>
+        </is>
+      </c>
+      <c r="H2" s="28" t="inlineStr">
+        <is>
+          <t>评价等级（每个等级对应目标）</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="27" t="inlineStr">
+        <is>
+          <t>权重
+比例</t>
+        </is>
+      </c>
+      <c r="N2" s="27" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="O2" s="29" t="inlineStr">
+        <is>
+          <t>完成情况</t>
+        </is>
+      </c>
+      <c r="P2" s="29" t="inlineStr">
+        <is>
+          <t>实际得分</t>
+        </is>
+      </c>
+      <c r="Q2" s="29" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14.65" customHeight="1">
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="8" t="n"/>
+      <c r="H3" s="30" t="inlineStr">
+        <is>
+          <t>A（120%）</t>
+        </is>
+      </c>
+      <c r="I3" s="30" t="inlineStr">
+        <is>
+          <t>B（100%）</t>
+        </is>
+      </c>
+      <c r="J3" s="30" t="inlineStr">
+        <is>
+          <t>C（90%）</t>
+        </is>
+      </c>
+      <c r="K3" s="30" t="inlineStr">
+        <is>
+          <t>D（80%）</t>
+        </is>
+      </c>
+      <c r="L3" s="30" t="inlineStr">
+        <is>
+          <t>E（0）</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
+      <c r="O3" s="8" t="n"/>
+      <c r="P3" s="8" t="n"/>
+      <c r="Q3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="217.5" customFormat="1" customHeight="1" s="1">
+      <c r="B4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="D4" s="10">
+        <f>VLOOKUP(E4,'[1]2026年上-人员清单'!$F:$N,9,0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>李涛</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Sandwich项目管理支持</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>1）连续氢化建设项目管理支持：
+目前项目已推进至 HAZOP 完成阶段。2026年将持续支持并协调 CFCT、IEPE 与 SW 各方，推进布局设计、工程采购、CE认证、测试验证等工作，做好跨团队沟通与协同，保障项目按计划整体推进。</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>完成年度目标，自评结合上级评价【加分上限为指标权重的20%】</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>自评+上级领导审核</t>
+        </is>
+      </c>
+      <c r="O4" s="15" t="inlineStr">
+        <is>
+          <t>作为国内项目管理支持，协调 CFCT、IEPE 与 UK Sandwich 三方，系统推动项目整体节奏，主要进展如下：
+• 已推动关闭三方之间 30 余项关键设计议题（含 PFD / P&amp;ID / URS 三大设计文件对齐、SE01 气液分离器方案闭环、CE-MD 认证范围确定、防爆区域划分方向确定等），主要设计文件基本齐备；
+• 建立并稳定运行中英双方的技术协作机制，通过双语《会议纪要跟踪表》系统跟踪超过 100 项议题，对英方问询、技术分歧、设计变更做到全过程可追溯；
+• 有效应对超临界流体安全阀泄放计算等前沿技术议题，组织国内技术团队与 UK 同行建立对等技术对话，避免项目在关键节点上被动等待；
+• 设计基线对齐工作 —— 汇总国内 33 项待澄清问题与 UK 一方 59 项 Risk Register 合并至统一跟踪；
+下半年计划：继续推动详细设计完成、主设备采购启动、CE 认证正式启动，为 2027 年 FAT 与现场开车目标铺路。项目整体节奏可控。</t>
+        </is>
+      </c>
+      <c r="P4" s="15" t="n"/>
+      <c r="Q4" s="15" t="inlineStr">
+        <is>
+          <t>项目按计划推进，超期风险已受控</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="145" customFormat="1" customHeight="1" s="1">
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>2）HPLC和冻干机建设项目管理支持：
+目前项目已完成可行性研究及投资框架梳理。2026年将持续支持并协调工程设备部与 SW 方，推进下阶段设计、长周期设备采购决策及相关配套事项对接，保障项目有序实施。</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>完成年度目标，自评结合上级评价【加分上限为指标权重的20%】</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="16" t="n"/>
+      <c r="N5" s="16" t="n"/>
+      <c r="O5" s="18" t="inlineStr">
+        <is>
+          <t>作为国内项目管理支持，协调工程设备部与 UK Sandwich 两方，系统推动制备色谱及冻干机改造项目节奏，主要进展如下：
+• 全程跟进英国侧可行性研究讲解及多轮专题会，推动方案布局与投资口径在英方与国内团队之间形成一致理解，可行性研究结论及投资框架已明确；
+• 汇总项目投资与进度信息，编制多版组合汇报材料，支撑汇报与下阶段决策沟通；
+• 持续跟进设备供货与方案变更确认，协调国内团队经验输入，并统筹色谱冻干改造与 C1 模块升级、高活实验室等配套事项的接口对接，避免各子项割裂推进；</t>
+        </is>
+      </c>
+      <c r="P5" s="15" t="n"/>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>项目处于早期阶段，按计划推进</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="87" customFormat="1" customHeight="1" s="1">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>3）902贴建项目管理支持：
+目前项目已完成东侧扩建可行性研究（2026年5月）。2026年将持续支持并协调工程设备部与 SW 方，推进概念设计、关键方案确认及与国内团队的信息闭环，确保项目按计划开展。</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>完成年度目标，自评结合上级评价【加分上限为指标权重的20%】</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>作为国内项目管理支持，协调工程设备部与 UK Sandwich 及设计方，系统推动 902 东侧扩建项目节奏，主要进展如下：
+• 全程参与可行性研究讲解会，整理中文详细纪要及对内通报材料，推动国内团队理解推荐方案及关键前提假设；
+• 协助完成投资量级、风险与总控计划的梳理解读，编制汇报材料，支撑扩建项目投资与进度决策；</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="15" t="inlineStr">
+        <is>
+          <t>项目处于早期阶段，按计划推进</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customFormat="1" customHeight="1" s="1">
+      <c r="B7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="D7" s="10">
+        <f>VLOOKUP(E7,'[1]2026年上-人员清单'!$F:$N,9,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>李涛</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Sandwich 相关支持任务</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>负责 Sandwich 站点年度预算申请、执行监控及回顾，并协调机器学习研讨小组，推动相关技术交流与协作落地</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>月概算和月回顾100%完成</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>100%＞完成率≥90%</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>90%＞完成率≥80%</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>80%＞完成率≥70%</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>完成率＜70%</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N7" s="14" t="inlineStr">
+        <is>
+          <t>自评+上级领导审核</t>
+        </is>
+      </c>
+      <c r="O7" s="18" t="inlineStr">
+        <is>
+          <t>承担 Sandwich 站点预算及机器学习研讨小组相关支持，主要进展如下：
+• 参与 Sandwich 站点年度预算申请、执行跟踪相关数据整理与内外沟通支持；
+• 协调机器学习研讨小组交流安排，推动相关技术议题按计划开展；</t>
+        </is>
+      </c>
+      <c r="P7" s="15" t="n"/>
+      <c r="Q7" s="15" t="inlineStr">
+        <is>
+          <t>月概算与月回顾按时 100% 完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customFormat="1" customHeight="1" s="1">
+      <c r="B8" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>4</v>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>5</v>
+      <c r="D8" s="31">
+        <f>VLOOKUP(E8,'[1]2026年上-人员清单'!$F:$N,9,0)</f>
+        <v/>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>6</v>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>李涛</t>
+        </is>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="3" t="s">
-        <v>7</v>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>重点工作</t>
+        </is>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>8</v>
+      <c r="G8" s="32" t="inlineStr">
+        <is>
+          <t>配合推进电算化等生产管理重点工作。
+支持生产管理重点工作的落实，全力推动，确保各项工作顺利开展。</t>
+        </is>
       </c>
-      <c r="O2" s="7" t="s">
-        <v>9</v>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>完成年度目标，自评结合上级评价【加分上限为指标权重的20%】</t>
+        </is>
       </c>
-      <c r="P2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="14.65" customHeight="1" spans="2:17">
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="217.5" spans="2:17">
-      <c r="B4" s="10">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="10" t="str">
-        <f>VLOOKUP(E4,'[1]2026年上-人员清单'!$F:$N,9,0)</f>
-        <v>集团生产管理办公室</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O4" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="145" spans="2:17">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="87" spans="2:17">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="80" customHeight="1" spans="2:17">
-      <c r="B7" s="10">
-        <v>2</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="10" t="str">
-        <f>VLOOKUP(E7,'[1]2026年上-人员清单'!$F:$N,9,0)</f>
-        <v>集团生产管理办公室</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="60" customHeight="1" spans="2:17">
-      <c r="B8" s="22">
-        <v>3</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="23" t="str">
-        <f>VLOOKUP(E8,'[1]2026年上-人员清单'!$F:$N,9,0)</f>
-        <v>集团生产管理办公室</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="25">
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="N8" s="26" t="s">
-        <v>22</v>
+      <c r="N8" s="33" t="inlineStr">
+        <is>
+          <t>自评+上级领导审核</t>
+        </is>
       </c>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15" t="s">
-        <v>41</v>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>承担生产管理 AI 应用推动相关工作，围绕重点方向梳理、供应商评估与跨部门协同，主要进展如下：
+• 系统梳理生产管理 6 大 AI 应用方向（涵盖 QC / 报告撰写 / 技术转移 / 设备管理 / 视觉合规 / 培训生成），编制思路方案与逐项落地推进方案，形成集团 AI 布局的横向蓝图；
+• 主导对智现未来、埃森哲、远景智能等潜在合作商的深度评估，输出内部评估报告，形成"多供应商组合、凯莱英自主主导"的合作思路；
+• 结合 DH1 动力站已有基础推进设备预测性维护 —— 完成和利时、信力共擎、埃森哲三方方案对比，主导埃森哲 PdM 会议后的总结与汇报编制，明确"信息整理 → 方案对齐 → PoC 启动"的推进节奏；
+• 与 IT 联合输出 6 方向工程化实施方案（含分工矩阵、Gantt 与 Sprint 表），并牵头 TJ4 生产看板在氨基酸项目按项目口径统计功能上的需求对接；
+• 配合电算化等生产管理其他数智化重点工作按上级安排推进。
+下半年计划：推动 1-2 个方向进入 PoC 阶段，同步完成设备预测性维护 4 类信息整理与方案对齐，为集团 AI 战略下一步决策提供实证。</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="n"/>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>按上级安排配合推进</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="M4:M6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F4:F6"/>
     <mergeCell ref="H2:L2"/>
-    <mergeCell ref="H4:L4"/>
+    <mergeCell ref="N4:N6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="C4:C6"/>
     <mergeCell ref="H5:L5"/>
-    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="G2:G3"/>
     <mergeCell ref="H8:L8"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="M4:M6"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="N4:N6"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>